--- a/project/MDK_V5/AT32F403ARGT7_Flash_Cfg_Update_analysis.xlsx
+++ b/project/MDK_V5/AT32F403ARGT7_Flash_Cfg_Update_analysis.xlsx
@@ -632,160 +632,160 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="53"/>
                 <c:pt idx="0">
-                  <c:v>14.61198043823242</c:v>
+                  <c:v>14.99571323394775</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.52796173095703</c:v>
+                  <c:v>13.46716690063477</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.61447525024414</c:v>
+                  <c:v>10.56677436828613</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.060348510742188</c:v>
+                  <c:v>8.024126052856445</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.753586292266846</c:v>
+                  <c:v>6.723235607147217</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.063704490661621</c:v>
+                  <c:v>5.040948390960693</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.193519592285156</c:v>
+                  <c:v>4.174674034118652</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.849009513854981</c:v>
+                  <c:v>3.831712245941162</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.801490783691406</c:v>
+                  <c:v>3.784407138824463</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.361943483352661</c:v>
+                  <c:v>3.346834897994995</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.332244396209717</c:v>
+                  <c:v>3.317269325256348</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.165929079055786</c:v>
+                  <c:v>3.1517014503479</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.007662296295166</c:v>
+                  <c:v>1.998639941215515</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.90668523311615</c:v>
+                  <c:v>1.898116707801819</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.787888646125794</c:v>
+                  <c:v>1.779853940010071</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.508716702461243</c:v>
+                  <c:v>1.501936554908752</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.259243845939636</c:v>
+                  <c:v>1.253584861755371</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.048379898071289</c:v>
+                  <c:v>1.043668508529663</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9919515252113342</c:v>
+                  <c:v>0.9874936938285828</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9711621403694153</c:v>
+                  <c:v>0.9667977690696716</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9236434698104858</c:v>
+                  <c:v>0.9194926619529724</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8790947794914246</c:v>
+                  <c:v>0.8751441240310669</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.6771405935287476</c:v>
+                  <c:v>0.67409747838974</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.6593210697174072</c:v>
+                  <c:v>0.6563581228256226</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6118024587631226</c:v>
+                  <c:v>0.6090530157089233</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5524041652679443</c:v>
+                  <c:v>0.5499216318130493</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5048854947090149</c:v>
+                  <c:v>0.5026165843009949</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.350449949502945</c:v>
+                  <c:v>0.3488750159740448</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.3445101082324982</c:v>
+                  <c:v>0.3429618775844574</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.2910516560077667</c:v>
+                  <c:v>0.2897436618804932</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.2791719734668732</c:v>
+                  <c:v>0.2779173851013184</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.2375931739807129</c:v>
+                  <c:v>0.2365254461765289</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1544355750083923</c:v>
+                  <c:v>0.1537415385246277</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.14255590736866</c:v>
+                  <c:v>0.1419152617454529</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.14255590736866</c:v>
+                  <c:v>0.1419152617454529</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.14255590736866</c:v>
+                  <c:v>0.1419152617454529</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1306762546300888</c:v>
+                  <c:v>0.1300889998674393</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1306762546300888</c:v>
+                  <c:v>0.1300889998674393</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1187965869903565</c:v>
+                  <c:v>0.1182627230882645</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1128567606210709</c:v>
+                  <c:v>0.1123495846986771</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1069169342517853</c:v>
+                  <c:v>0.1064364463090897</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1069169342517853</c:v>
+                  <c:v>0.1064364463090897</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1069169342517853</c:v>
+                  <c:v>0.1064364463090897</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.09503727406263351</c:v>
+                  <c:v>0.09461017698049545</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.08909744024276733</c:v>
+                  <c:v>0.08869703859090805</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.08909744024276733</c:v>
+                  <c:v>0.08869703859090805</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.07721778750419617</c:v>
+                  <c:v>0.07687076926231384</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.05345846712589264</c:v>
+                  <c:v>0.05321822315454483</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.02375931851565838</c:v>
+                  <c:v>0.02365254424512386</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.02375931851565838</c:v>
+                  <c:v>0.02365254424512386</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.01187965925782919</c:v>
+                  <c:v>0.01182627212256193</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.01187965925782919</c:v>
+                  <c:v>0.01182627212256193</c:v>
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0</c:v>
@@ -1336,13 +1336,13 @@
         <v>1054</v>
       </c>
       <c r="D6" s="1">
-        <v>4920</v>
+        <v>5072</v>
       </c>
       <c r="E6" s="1">
-        <v>2660</v>
+        <v>2758</v>
       </c>
       <c r="F6" s="1">
-        <v>2260</v>
+        <v>2314</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1697,19 +1697,19 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>14.61198043823242</v>
+        <v>14.99571323394775</v>
       </c>
       <c r="C3" s="1">
-        <v>4920</v>
+        <v>5072</v>
       </c>
       <c r="D3" s="1">
         <v>1054</v>
       </c>
       <c r="E3" s="1">
-        <v>2660</v>
+        <v>2758</v>
       </c>
       <c r="F3" s="1">
-        <v>2260</v>
+        <v>2314</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>13.52796173095703</v>
+        <v>13.46716690063477</v>
       </c>
       <c r="C4" s="1">
         <v>4555</v>
@@ -1749,7 +1749,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>10.61447525024414</v>
+        <v>10.56677436828613</v>
       </c>
       <c r="C5" s="1">
         <v>3574</v>
@@ -1775,7 +1775,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>8.060348510742188</v>
+        <v>8.024126052856445</v>
       </c>
       <c r="C6" s="1">
         <v>2714</v>
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>6.753586292266846</v>
+        <v>6.723235607147217</v>
       </c>
       <c r="C7" s="1">
         <v>2274</v>
@@ -1827,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>5.063704490661621</v>
+        <v>5.040948390960693</v>
       </c>
       <c r="C8" s="1">
         <v>1705</v>
@@ -1853,7 +1853,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2">
-        <v>4.193519592285156</v>
+        <v>4.174674034118652</v>
       </c>
       <c r="C9" s="1">
         <v>1412</v>
@@ -1879,7 +1879,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2">
-        <v>3.849009513854981</v>
+        <v>3.831712245941162</v>
       </c>
       <c r="C10" s="1">
         <v>1296</v>
@@ -1905,7 +1905,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>3.801490783691406</v>
+        <v>3.784407138824463</v>
       </c>
       <c r="C11" s="1">
         <v>1280</v>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>3.361943483352661</v>
+        <v>3.346834897994995</v>
       </c>
       <c r="C12" s="1">
         <v>1132</v>
@@ -1957,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>3.332244396209717</v>
+        <v>3.317269325256348</v>
       </c>
       <c r="C13" s="1">
         <v>1122</v>
@@ -1983,7 +1983,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>3.165929079055786</v>
+        <v>3.1517014503479</v>
       </c>
       <c r="C14" s="1">
         <v>1066</v>
@@ -2009,7 +2009,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="2">
-        <v>2.007662296295166</v>
+        <v>1.998639941215515</v>
       </c>
       <c r="C15" s="1">
         <v>676</v>
@@ -2035,7 +2035,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="2">
-        <v>1.90668523311615</v>
+        <v>1.898116707801819</v>
       </c>
       <c r="C16" s="1">
         <v>642</v>
@@ -2061,7 +2061,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <v>1.787888646125794</v>
+        <v>1.779853940010071</v>
       </c>
       <c r="C17" s="1">
         <v>602</v>
@@ -2087,7 +2087,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="2">
-        <v>1.508716702461243</v>
+        <v>1.501936554908752</v>
       </c>
       <c r="C18" s="1">
         <v>508</v>
@@ -2113,7 +2113,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="2">
-        <v>1.259243845939636</v>
+        <v>1.253584861755371</v>
       </c>
       <c r="C19" s="1">
         <v>424</v>
@@ -2139,7 +2139,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="2">
-        <v>1.048379898071289</v>
+        <v>1.043668508529663</v>
       </c>
       <c r="C20" s="1">
         <v>353</v>
@@ -2165,7 +2165,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="2">
-        <v>0.9919515252113342</v>
+        <v>0.9874936938285828</v>
       </c>
       <c r="C21" s="1">
         <v>334</v>
@@ -2191,7 +2191,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9711621403694153</v>
+        <v>0.9667977690696716</v>
       </c>
       <c r="C22" s="1">
         <v>327</v>
@@ -2217,7 +2217,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9236434698104858</v>
+        <v>0.9194926619529724</v>
       </c>
       <c r="C23" s="1">
         <v>311</v>
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8790947794914246</v>
+        <v>0.8751441240310669</v>
       </c>
       <c r="C24" s="1">
         <v>296</v>
@@ -2269,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.6771405935287476</v>
+        <v>0.67409747838974</v>
       </c>
       <c r="C25" s="1">
         <v>228</v>
@@ -2295,7 +2295,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.6593210697174072</v>
+        <v>0.6563581228256226</v>
       </c>
       <c r="C26" s="1">
         <v>222</v>
@@ -2321,7 +2321,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6118024587631226</v>
+        <v>0.6090530157089233</v>
       </c>
       <c r="C27" s="1">
         <v>206</v>
@@ -2347,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.5524041652679443</v>
+        <v>0.5499216318130493</v>
       </c>
       <c r="C28" s="1">
         <v>186</v>
@@ -2373,7 +2373,7 @@
         <v>12</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5048854947090149</v>
+        <v>0.5026165843009949</v>
       </c>
       <c r="C29" s="1">
         <v>170</v>
@@ -2399,7 +2399,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.350449949502945</v>
+        <v>0.3488750159740448</v>
       </c>
       <c r="C30" s="1">
         <v>118</v>
@@ -2425,7 +2425,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.3445101082324982</v>
+        <v>0.3429618775844574</v>
       </c>
       <c r="C31" s="1">
         <v>116</v>
@@ -2451,7 +2451,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.2910516560077667</v>
+        <v>0.2897436618804932</v>
       </c>
       <c r="C32" s="1">
         <v>98</v>
@@ -2477,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>0.2791719734668732</v>
+        <v>0.2779173851013184</v>
       </c>
       <c r="C33" s="1">
         <v>94</v>
@@ -2503,7 +2503,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>0.2375931739807129</v>
+        <v>0.2365254461765289</v>
       </c>
       <c r="C34" s="1">
         <v>80</v>
@@ -2529,7 +2529,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1544355750083923</v>
+        <v>0.1537415385246277</v>
       </c>
       <c r="C35" s="1">
         <v>52</v>
@@ -2555,7 +2555,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>0.14255590736866</v>
+        <v>0.1419152617454529</v>
       </c>
       <c r="C36" s="1">
         <v>48</v>
@@ -2581,7 +2581,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>0.14255590736866</v>
+        <v>0.1419152617454529</v>
       </c>
       <c r="C37" s="1">
         <v>48</v>
@@ -2607,7 +2607,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>0.14255590736866</v>
+        <v>0.1419152617454529</v>
       </c>
       <c r="C38" s="1">
         <v>48</v>
@@ -2633,7 +2633,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1306762546300888</v>
+        <v>0.1300889998674393</v>
       </c>
       <c r="C39" s="1">
         <v>44</v>
@@ -2659,7 +2659,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1306762546300888</v>
+        <v>0.1300889998674393</v>
       </c>
       <c r="C40" s="1">
         <v>44</v>
@@ -2685,7 +2685,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1187965869903565</v>
+        <v>0.1182627230882645</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -2711,7 +2711,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1128567606210709</v>
+        <v>0.1123495846986771</v>
       </c>
       <c r="C42" s="1">
         <v>38</v>
@@ -2737,7 +2737,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1069169342517853</v>
+        <v>0.1064364463090897</v>
       </c>
       <c r="C43" s="1">
         <v>36</v>
@@ -2763,7 +2763,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1069169342517853</v>
+        <v>0.1064364463090897</v>
       </c>
       <c r="C44" s="1">
         <v>36</v>
@@ -2789,7 +2789,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1069169342517853</v>
+        <v>0.1064364463090897</v>
       </c>
       <c r="C45" s="1">
         <v>36</v>
@@ -2815,7 +2815,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0.09503727406263351</v>
+        <v>0.09461017698049545</v>
       </c>
       <c r="C46" s="1">
         <v>32</v>
@@ -2841,7 +2841,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.08909744024276733</v>
+        <v>0.08869703859090805</v>
       </c>
       <c r="C47" s="1">
         <v>30</v>
@@ -2867,7 +2867,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.08909744024276733</v>
+        <v>0.08869703859090805</v>
       </c>
       <c r="C48" s="1">
         <v>30</v>
@@ -2893,7 +2893,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.07721778750419617</v>
+        <v>0.07687076926231384</v>
       </c>
       <c r="C49" s="1">
         <v>26</v>
@@ -2919,7 +2919,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.05345846712589264</v>
+        <v>0.05321822315454483</v>
       </c>
       <c r="C50" s="1">
         <v>18</v>
@@ -2945,7 +2945,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.02375931851565838</v>
+        <v>0.02365254424512386</v>
       </c>
       <c r="C51" s="1">
         <v>8</v>
@@ -2971,7 +2971,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.02375931851565838</v>
+        <v>0.02365254424512386</v>
       </c>
       <c r="C52" s="1">
         <v>8</v>
@@ -2997,7 +2997,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="2">
-        <v>0.01187965925782919</v>
+        <v>0.01182627212256193</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.01187965925782919</v>
+        <v>0.01182627212256193</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>

--- a/project/MDK_V5/AT32F403ARGT7_Flash_Cfg_Update_analysis.xlsx
+++ b/project/MDK_V5/AT32F403ARGT7_Flash_Cfg_Update_analysis.xlsx
@@ -500,31 +500,31 @@
                   <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>system_main.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>at32f403a_407_wk_config.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>at32f403a_407_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>at32f403a_407_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>log.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>freertos_app.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>system_main.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>list.o</c:v>
@@ -632,160 +632,160 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="53"/>
                 <c:pt idx="0">
-                  <c:v>14.99571323394775</c:v>
+                  <c:v>15.58939743041992</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.46716690063477</c:v>
+                  <c:v>13.03887367248535</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.56677436828613</c:v>
+                  <c:v>10.23072052001953</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.024126052856445</c:v>
+                  <c:v>7.768935680389404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.723235607147217</c:v>
+                  <c:v>6.509417533874512</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.040948390960693</c:v>
+                  <c:v>4.880631923675537</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.174674034118652</c:v>
+                  <c:v>4.041907787322998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.831712245941162</c:v>
+                  <c:v>3.709852933883667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.784407138824463</c:v>
+                  <c:v>3.664052248001099</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.346834897994995</c:v>
+                  <c:v>3.24039626121521</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.317269325256348</c:v>
+                  <c:v>3.21177077293396</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.1517014503479</c:v>
+                  <c:v>3.051468372344971</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.998639941215515</c:v>
+                  <c:v>2.999942779541016</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.898116707801819</c:v>
+                  <c:v>1.935077548027039</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.779853940010071</c:v>
+                  <c:v>1.837751150131226</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.501936554908752</c:v>
+                  <c:v>1.723249554634094</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.253584861755371</c:v>
+                  <c:v>1.45417070388794</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.043668508529663</c:v>
+                  <c:v>1.213717341423035</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9874936938285828</c:v>
+                  <c:v>1.01047694683075</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9667977690696716</c:v>
+                  <c:v>0.9560886025428772</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9194926619529724</c:v>
+                  <c:v>0.9360508322715759</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8751441240310669</c:v>
+                  <c:v>0.8473120927810669</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.67409747838974</c:v>
+                  <c:v>0.6526592969894409</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.6563581228256226</c:v>
+                  <c:v>0.6354840397834778</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6090530157089233</c:v>
+                  <c:v>0.5896834135055542</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5499216318130493</c:v>
+                  <c:v>0.5324326157569885</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.5026165843009949</c:v>
+                  <c:v>0.4866319298744202</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.3488750159740448</c:v>
+                  <c:v>0.3377798199653626</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.3429618775844574</c:v>
+                  <c:v>0.3320547342300415</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.2897436618804932</c:v>
+                  <c:v>0.2805289924144745</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.2779173851013184</c:v>
+                  <c:v>0.2690788209438324</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.2365254461765289</c:v>
+                  <c:v>0.2290032655000687</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1537415385246277</c:v>
+                  <c:v>0.1488521248102188</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1419152617454529</c:v>
+                  <c:v>0.1374019533395767</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1419152617454529</c:v>
+                  <c:v>0.1374019533395767</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1419152617454529</c:v>
+                  <c:v>0.1374019533395767</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1300889998674393</c:v>
+                  <c:v>0.1259517967700958</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1300889998674393</c:v>
+                  <c:v>0.1259517967700958</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1182627230882645</c:v>
+                  <c:v>0.1145016327500343</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1123495846986771</c:v>
+                  <c:v>0.1087765470147133</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1064364463090897</c:v>
+                  <c:v>0.1030514687299728</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1064364463090897</c:v>
+                  <c:v>0.1030514687299728</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1064364463090897</c:v>
+                  <c:v>0.1030514687299728</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.09461017698049545</c:v>
+                  <c:v>0.09160130470991135</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.08869703859090805</c:v>
+                  <c:v>0.0858762264251709</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.08869703859090805</c:v>
+                  <c:v>0.0858762264251709</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.07687076926231384</c:v>
+                  <c:v>0.07442606240510941</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.05321822315454483</c:v>
+                  <c:v>0.05152573436498642</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.02365254424512386</c:v>
+                  <c:v>0.02290032617747784</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.02365254424512386</c:v>
+                  <c:v>0.02290032617747784</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.01182627212256193</c:v>
+                  <c:v>0.01145016308873892</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.01182627212256193</c:v>
+                  <c:v>0.01145016308873892</c:v>
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>0</c:v>
@@ -1336,13 +1336,13 @@
         <v>1054</v>
       </c>
       <c r="D6" s="1">
-        <v>5072</v>
+        <v>5446</v>
       </c>
       <c r="E6" s="1">
-        <v>2758</v>
+        <v>3078</v>
       </c>
       <c r="F6" s="1">
-        <v>2314</v>
+        <v>2368</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1570,13 +1570,13 @@
         <v>4</v>
       </c>
       <c r="D15" s="1">
-        <v>311</v>
+        <v>1048</v>
       </c>
       <c r="E15" s="1">
-        <v>214</v>
+        <v>674</v>
       </c>
       <c r="F15" s="1">
-        <v>97</v>
+        <v>374</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1697,19 +1697,19 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>14.99571323394775</v>
+        <v>15.58939743041992</v>
       </c>
       <c r="C3" s="1">
-        <v>5072</v>
+        <v>5446</v>
       </c>
       <c r="D3" s="1">
         <v>1054</v>
       </c>
       <c r="E3" s="1">
-        <v>2758</v>
+        <v>3078</v>
       </c>
       <c r="F3" s="1">
-        <v>2314</v>
+        <v>2368</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>13.46716690063477</v>
+        <v>13.03887367248535</v>
       </c>
       <c r="C4" s="1">
         <v>4555</v>
@@ -1749,7 +1749,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>10.56677436828613</v>
+        <v>10.23072052001953</v>
       </c>
       <c r="C5" s="1">
         <v>3574</v>
@@ -1775,7 +1775,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>8.024126052856445</v>
+        <v>7.768935680389404</v>
       </c>
       <c r="C6" s="1">
         <v>2714</v>
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>6.723235607147217</v>
+        <v>6.509417533874512</v>
       </c>
       <c r="C7" s="1">
         <v>2274</v>
@@ -1827,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>5.040948390960693</v>
+        <v>4.880631923675537</v>
       </c>
       <c r="C8" s="1">
         <v>1705</v>
@@ -1853,7 +1853,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2">
-        <v>4.174674034118652</v>
+        <v>4.041907787322998</v>
       </c>
       <c r="C9" s="1">
         <v>1412</v>
@@ -1879,7 +1879,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2">
-        <v>3.831712245941162</v>
+        <v>3.709852933883667</v>
       </c>
       <c r="C10" s="1">
         <v>1296</v>
@@ -1905,7 +1905,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>3.784407138824463</v>
+        <v>3.664052248001099</v>
       </c>
       <c r="C11" s="1">
         <v>1280</v>
@@ -1931,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>3.346834897994995</v>
+        <v>3.24039626121521</v>
       </c>
       <c r="C12" s="1">
         <v>1132</v>
@@ -1957,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>3.317269325256348</v>
+        <v>3.21177077293396</v>
       </c>
       <c r="C13" s="1">
         <v>1122</v>
@@ -1983,7 +1983,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>3.1517014503479</v>
+        <v>3.051468372344971</v>
       </c>
       <c r="C14" s="1">
         <v>1066</v>
@@ -2006,45 +2006,45 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>1.998639941215515</v>
+        <v>2.999942779541016</v>
       </c>
       <c r="C15" s="1">
-        <v>676</v>
+        <v>1048</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="2">
-        <v>1.898116707801819</v>
+        <v>1.935077548027039</v>
       </c>
       <c r="C16" s="1">
-        <v>642</v>
+        <v>676</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>642</v>
+        <v>676</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2058,25 +2058,25 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2">
-        <v>1.779853940010071</v>
+        <v>1.837751150131226</v>
       </c>
       <c r="C17" s="1">
-        <v>602</v>
+        <v>642</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>582</v>
+        <v>642</v>
       </c>
       <c r="F17" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -2084,25 +2084,25 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2">
-        <v>1.501936554908752</v>
+        <v>1.723249554634094</v>
       </c>
       <c r="C18" s="1">
-        <v>508</v>
+        <v>602</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1">
-        <v>508</v>
+        <v>582</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -2110,132 +2110,132 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2">
-        <v>1.253584861755371</v>
+        <v>1.45417070388794</v>
       </c>
       <c r="C19" s="1">
-        <v>424</v>
+        <v>508</v>
       </c>
       <c r="D19" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>36</v>
+        <v>508</v>
       </c>
       <c r="F19" s="1">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B20" s="2">
-        <v>1.043668508529663</v>
+        <v>1.213717341423035</v>
       </c>
       <c r="C20" s="1">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="D20" s="1">
-        <v>88</v>
+        <v>4096</v>
       </c>
       <c r="E20" s="1">
-        <v>336</v>
+        <v>36</v>
       </c>
       <c r="F20" s="1">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>88</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2">
-        <v>0.9874936938285828</v>
+        <v>1.01047694683075</v>
       </c>
       <c r="C21" s="1">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9667977690696716</v>
+        <v>0.9560886025428772</v>
       </c>
       <c r="C22" s="1">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D22" s="1">
-        <v>1724</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="F22" s="1">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>1724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9194926619529724</v>
+        <v>0.9360508322715759</v>
       </c>
       <c r="C23" s="1">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="D23" s="1">
-        <v>4</v>
+        <v>1724</v>
       </c>
       <c r="E23" s="1">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="F23" s="1">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2243,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8751441240310669</v>
+        <v>0.8473120927810669</v>
       </c>
       <c r="C24" s="1">
         <v>296</v>
@@ -2269,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.67409747838974</v>
+        <v>0.6526592969894409</v>
       </c>
       <c r="C25" s="1">
         <v>228</v>
@@ -2295,7 +2295,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.6563581228256226</v>
+        <v>0.6354840397834778</v>
       </c>
       <c r="C26" s="1">
         <v>222</v>
@@ -2321,7 +2321,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6090530157089233</v>
+        <v>0.5896834135055542</v>
       </c>
       <c r="C27" s="1">
         <v>206</v>
@@ -2347,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.5499216318130493</v>
+        <v>0.5324326157569885</v>
       </c>
       <c r="C28" s="1">
         <v>186</v>
@@ -2373,7 +2373,7 @@
         <v>12</v>
       </c>
       <c r="B29" s="2">
-        <v>0.5026165843009949</v>
+        <v>0.4866319298744202</v>
       </c>
       <c r="C29" s="1">
         <v>170</v>
@@ -2399,7 +2399,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.3488750159740448</v>
+        <v>0.3377798199653626</v>
       </c>
       <c r="C30" s="1">
         <v>118</v>
@@ -2425,7 +2425,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.3429618775844574</v>
+        <v>0.3320547342300415</v>
       </c>
       <c r="C31" s="1">
         <v>116</v>
@@ -2451,7 +2451,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.2897436618804932</v>
+        <v>0.2805289924144745</v>
       </c>
       <c r="C32" s="1">
         <v>98</v>
@@ -2477,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>0.2779173851013184</v>
+        <v>0.2690788209438324</v>
       </c>
       <c r="C33" s="1">
         <v>94</v>
@@ -2503,7 +2503,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>0.2365254461765289</v>
+        <v>0.2290032655000687</v>
       </c>
       <c r="C34" s="1">
         <v>80</v>
@@ -2529,7 +2529,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1537415385246277</v>
+        <v>0.1488521248102188</v>
       </c>
       <c r="C35" s="1">
         <v>52</v>
@@ -2555,7 +2555,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1419152617454529</v>
+        <v>0.1374019533395767</v>
       </c>
       <c r="C36" s="1">
         <v>48</v>
@@ -2581,7 +2581,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>0.1419152617454529</v>
+        <v>0.1374019533395767</v>
       </c>
       <c r="C37" s="1">
         <v>48</v>
@@ -2607,7 +2607,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>0.1419152617454529</v>
+        <v>0.1374019533395767</v>
       </c>
       <c r="C38" s="1">
         <v>48</v>
@@ -2633,7 +2633,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1300889998674393</v>
+        <v>0.1259517967700958</v>
       </c>
       <c r="C39" s="1">
         <v>44</v>
@@ -2659,7 +2659,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1300889998674393</v>
+        <v>0.1259517967700958</v>
       </c>
       <c r="C40" s="1">
         <v>44</v>
@@ -2685,7 +2685,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1182627230882645</v>
+        <v>0.1145016327500343</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -2711,7 +2711,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1123495846986771</v>
+        <v>0.1087765470147133</v>
       </c>
       <c r="C42" s="1">
         <v>38</v>
@@ -2737,7 +2737,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1064364463090897</v>
+        <v>0.1030514687299728</v>
       </c>
       <c r="C43" s="1">
         <v>36</v>
@@ -2763,7 +2763,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1064364463090897</v>
+        <v>0.1030514687299728</v>
       </c>
       <c r="C44" s="1">
         <v>36</v>
@@ -2789,7 +2789,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1064364463090897</v>
+        <v>0.1030514687299728</v>
       </c>
       <c r="C45" s="1">
         <v>36</v>
@@ -2815,7 +2815,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0.09461017698049545</v>
+        <v>0.09160130470991135</v>
       </c>
       <c r="C46" s="1">
         <v>32</v>
@@ -2841,7 +2841,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.08869703859090805</v>
+        <v>0.0858762264251709</v>
       </c>
       <c r="C47" s="1">
         <v>30</v>
@@ -2867,7 +2867,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.08869703859090805</v>
+        <v>0.0858762264251709</v>
       </c>
       <c r="C48" s="1">
         <v>30</v>
@@ -2893,7 +2893,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.07687076926231384</v>
+        <v>0.07442606240510941</v>
       </c>
       <c r="C49" s="1">
         <v>26</v>
@@ -2919,7 +2919,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.05321822315454483</v>
+        <v>0.05152573436498642</v>
       </c>
       <c r="C50" s="1">
         <v>18</v>
@@ -2945,7 +2945,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.02365254424512386</v>
+        <v>0.02290032617747784</v>
       </c>
       <c r="C51" s="1">
         <v>8</v>
@@ -2971,7 +2971,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.02365254424512386</v>
+        <v>0.02290032617747784</v>
       </c>
       <c r="C52" s="1">
         <v>8</v>
@@ -2997,7 +2997,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="2">
-        <v>0.01182627212256193</v>
+        <v>0.01145016308873892</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.01182627212256193</v>
+        <v>0.01145016308873892</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
